--- a/Documents/Business Plan Tuc Tuc électrique à TAMATAVE.xlsx
+++ b/Documents/Business Plan Tuc Tuc électrique à TAMATAVE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2 PROJETS\Travails\Entreprise 1\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D477DAE-14C9-46EC-AA40-4F64AD82B19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA81C28-2C1C-42FD-B5F8-154D28BC5AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{46899F27-FDE4-1040-992F-FC242FEDCC9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{46899F27-FDE4-1040-992F-FC242FEDCC9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Lancement" sheetId="1" r:id="rId1"/>
@@ -2021,6 +2021,105 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2039,175 +2138,76 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="8" fillId="13" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="13" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="13" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="13" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3655,38 +3655,38 @@
       <c r="C1" s="27">
         <v>4450</v>
       </c>
-      <c r="D1" s="144" t="s">
+      <c r="D1" s="177" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="145"/>
-      <c r="G1" s="147" t="s">
+      <c r="E1" s="178"/>
+      <c r="G1" s="180" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="148"/>
-      <c r="L1" s="152" t="s">
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="181"/>
+      <c r="L1" s="184" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="184"/>
+      <c r="O1" s="184"/>
+      <c r="P1" s="184"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="155"/>
-      <c r="B2" s="155"/>
-      <c r="C2" s="156"/>
+      <c r="A2" s="175"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="176"/>
       <c r="D2" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="154" t="s">
+      <c r="G2" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="154"/>
+      <c r="H2" s="145"/>
       <c r="I2" s="29">
         <f>5000*30</f>
         <v>150000</v>
@@ -3695,11 +3695,11 @@
         <f>I2/$C$1</f>
         <v>33.707865168539328</v>
       </c>
-      <c r="L2" s="151" t="s">
+      <c r="L2" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
+      <c r="M2" s="183"/>
+      <c r="N2" s="183"/>
       <c r="O2" s="25" t="s">
         <v>7</v>
       </c>
@@ -3708,11 +3708,11 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="153" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
+      <c r="A3" s="161" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
       <c r="D3" s="11">
         <v>17000000</v>
       </c>
@@ -3721,10 +3721,10 @@
         <v>3820.2247191011238</v>
       </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="154" t="s">
+      <c r="G3" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="154"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="29">
         <v>100000</v>
       </c>
@@ -3732,11 +3732,11 @@
         <f>I3/$C$1</f>
         <v>22.471910112359552</v>
       </c>
-      <c r="L3" s="150" t="s">
+      <c r="L3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="150"/>
-      <c r="N3" s="150"/>
+      <c r="M3" s="167"/>
+      <c r="N3" s="167"/>
       <c r="O3" s="3">
         <v>200000</v>
       </c>
@@ -3746,11 +3746,11 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="153"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="161"/>
       <c r="D4" s="11">
         <v>66000</v>
       </c>
@@ -3758,10 +3758,10 @@
         <f>D4/$C$1</f>
         <v>14.831460674157304</v>
       </c>
-      <c r="G4" s="154" t="s">
+      <c r="G4" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="154"/>
+      <c r="H4" s="145"/>
       <c r="I4" s="29">
         <v>65000</v>
       </c>
@@ -3769,11 +3769,11 @@
         <f>I4/$C$1</f>
         <v>14.606741573033707</v>
       </c>
-      <c r="L4" s="150" t="s">
+      <c r="L4" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="150"/>
-      <c r="N4" s="150"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
       <c r="O4" s="3">
         <f>54000*3</f>
         <v>162000</v>
@@ -3784,11 +3784,11 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="161" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
       <c r="D5" s="11">
         <v>50000</v>
       </c>
@@ -3796,10 +3796,10 @@
         <f>D5/$C$1</f>
         <v>11.235955056179776</v>
       </c>
-      <c r="G5" s="154" t="s">
+      <c r="G5" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="154"/>
+      <c r="H5" s="145"/>
       <c r="I5" s="29">
         <f>(D4*5%)*26</f>
         <v>85800</v>
@@ -3808,11 +3808,11 @@
         <f>I5/$C$1</f>
         <v>19.280898876404493</v>
       </c>
-      <c r="L5" s="150" t="s">
+      <c r="L5" s="167" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="167"/>
       <c r="O5" s="3">
         <v>100000</v>
       </c>
@@ -3822,11 +3822,11 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
       <c r="D6" s="11">
         <f>(D4*26)</f>
         <v>1716000</v>
@@ -3835,10 +3835,10 @@
         <f>D6/$C$1</f>
         <v>385.61797752808991</v>
       </c>
-      <c r="G6" s="146" t="s">
+      <c r="G6" s="179" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="146"/>
+      <c r="H6" s="179"/>
       <c r="I6" s="19">
         <f>SUM(I1:I5)</f>
         <v>400800</v>
@@ -3847,11 +3847,11 @@
         <f>I6/$C$1</f>
         <v>90.067415730337075</v>
       </c>
-      <c r="L6" s="150" t="s">
+      <c r="L6" s="167" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="150"/>
-      <c r="N6" s="150"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
       <c r="O6" s="3">
         <v>300000</v>
       </c>
@@ -3861,11 +3861,11 @@
       </c>
     </row>
     <row r="7" spans="1:21" s="14" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="161" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="153"/>
-      <c r="C7" s="153"/>
+      <c r="B7" s="161"/>
+      <c r="C7" s="161"/>
       <c r="D7" s="11">
         <f>(D4*26)+(D5*4)</f>
         <v>1916000</v>
@@ -3875,11 +3875,11 @@
         <v>430.56179775280901</v>
       </c>
       <c r="K7" s="44"/>
-      <c r="L7" s="150" t="s">
+      <c r="L7" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="150"/>
-      <c r="N7" s="150"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
       <c r="O7" s="3"/>
       <c r="P7" s="4">
         <f t="shared" si="0"/>
@@ -3887,12 +3887,11 @@
       </c>
     </row>
     <row r="8" spans="1:21" s="14" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="F8" s="149" t="s">
+      <c r="F8" s="182" t="s">
         <v>161</v>
       </c>
-      <c r="G8" s="149"/>
-      <c r="H8" s="149"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
       <c r="I8" s="18">
         <f>('Crédit Banque'!B7)/7</f>
         <v>1505952.3809523808</v>
@@ -3902,11 +3901,11 @@
         <v>338.41626538255747</v>
       </c>
       <c r="K8" s="44"/>
-      <c r="L8" s="168" t="s">
+      <c r="L8" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="169"/>
-      <c r="N8" s="170"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="174"/>
       <c r="O8" s="19">
         <f>SUM(O3:O7)</f>
         <v>762000</v>
@@ -3924,79 +3923,79 @@
       <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:21" s="14" customFormat="1" ht="16.05" customHeight="1" thickBot="1">
-      <c r="A10" s="178" t="s">
+      <c r="A10" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="179"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="179"/>
-      <c r="E10" s="179"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="179"/>
-      <c r="H10" s="179"/>
-      <c r="I10" s="179"/>
-      <c r="J10" s="179"/>
-      <c r="K10" s="179"/>
-      <c r="L10" s="179"/>
-      <c r="M10" s="180"/>
-      <c r="O10" s="161" t="s">
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="154"/>
+      <c r="O10" s="164" t="s">
         <v>37</v>
       </c>
-      <c r="P10" s="162"/>
-      <c r="Q10" s="162"/>
-      <c r="R10" s="162"/>
-      <c r="S10" s="163"/>
+      <c r="P10" s="165"/>
+      <c r="Q10" s="165"/>
+      <c r="R10" s="165"/>
+      <c r="S10" s="166"/>
     </row>
     <row r="11" spans="1:21" ht="28.05" customHeight="1">
-      <c r="A11" s="157" t="s">
+      <c r="A11" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="181" t="s">
+      <c r="B11" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="183" t="s">
+      <c r="C11" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="171" t="s">
+      <c r="D11" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="171"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="172" t="s">
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="146" t="s">
         <v>116</v>
       </c>
-      <c r="L11" s="174" t="s">
+      <c r="L11" s="148" t="s">
         <v>163</v>
       </c>
-      <c r="M11" s="176" t="s">
+      <c r="M11" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="N11" s="167"/>
-      <c r="O11" s="157" t="s">
+      <c r="N11" s="171"/>
+      <c r="O11" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="P11" s="159" t="s">
+      <c r="P11" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="Q11" s="164" t="s">
+      <c r="Q11" s="168" t="s">
         <v>22</v>
       </c>
-      <c r="R11" s="164" t="s">
+      <c r="R11" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="S11" s="165" t="s">
+      <c r="S11" s="169" t="s">
         <v>24</v>
       </c>
       <c r="U11" s="17"/>
     </row>
     <row r="12" spans="1:21" ht="46.8">
-      <c r="A12" s="158"/>
-      <c r="B12" s="182"/>
-      <c r="C12" s="184"/>
+      <c r="A12" s="156"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="160"/>
       <c r="D12" s="13" t="s">
         <v>31</v>
       </c>
@@ -4022,15 +4021,15 @@
       <c r="J12" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="K12" s="173"/>
-      <c r="L12" s="175"/>
-      <c r="M12" s="177"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="158"/>
-      <c r="P12" s="160"/>
-      <c r="Q12" s="159"/>
-      <c r="R12" s="159"/>
-      <c r="S12" s="166"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="149"/>
+      <c r="M12" s="151"/>
+      <c r="N12" s="171"/>
+      <c r="O12" s="156"/>
+      <c r="P12" s="163"/>
+      <c r="Q12" s="162"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="170"/>
       <c r="U12" s="17"/>
     </row>
     <row r="13" spans="1:21">
@@ -6400,16 +6399,22 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="P11:P12"/>
     <mergeCell ref="O10:S10"/>
@@ -6421,22 +6426,16 @@
     <mergeCell ref="S11:S12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="L8:N8"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6466,17 +6465,17 @@
         <v>4450</v>
       </c>
       <c r="C1" s="61"/>
-      <c r="D1" s="188" t="s">
+      <c r="D1" s="204" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="188"/>
+      <c r="E1" s="204"/>
     </row>
     <row r="2" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="205" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="205"/>
       <c r="D2" s="64" t="s">
         <v>7</v>
       </c>
@@ -6485,11 +6484,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.05" customHeight="1" thickBot="1">
-      <c r="A3" s="187" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="187"/>
-      <c r="C3" s="187"/>
+      <c r="A3" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="206"/>
+      <c r="C3" s="206"/>
       <c r="D3" s="66">
         <v>17000000</v>
       </c>
@@ -6504,34 +6503,34 @@
       <c r="C4" s="68"/>
       <c r="D4" s="68"/>
       <c r="E4" s="68"/>
-      <c r="G4" s="189" t="s">
+      <c r="G4" s="185" t="s">
         <v>166</v>
       </c>
-      <c r="H4" s="190"/>
-      <c r="I4" s="191"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="187"/>
     </row>
     <row r="5" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A5" s="186" t="s">
+      <c r="A5" s="205" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
       <c r="D5" s="64" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="192"/>
-      <c r="H5" s="193"/>
-      <c r="I5" s="194"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="189"/>
+      <c r="I5" s="190"/>
     </row>
     <row r="6" spans="1:9" ht="21" customHeight="1">
-      <c r="A6" s="187">
+      <c r="A6" s="206">
         <v>36</v>
       </c>
-      <c r="B6" s="187"/>
-      <c r="C6" s="187"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
       <c r="D6" s="66">
         <f>$D$3/$A$6</f>
         <v>472222.22222222225</v>
@@ -6540,23 +6539,23 @@
         <f>$D$6/$B$1</f>
         <v>106.11735330836456</v>
       </c>
-      <c r="G6" s="192"/>
-      <c r="H6" s="193"/>
-      <c r="I6" s="194"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="190"/>
     </row>
     <row r="7" spans="1:9" ht="16.05" customHeight="1">
-      <c r="G7" s="192"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="194"/>
+      <c r="G7" s="188"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="190"/>
     </row>
     <row r="8" spans="1:9" ht="16.05" customHeight="1">
       <c r="A8" s="32">
         <v>46022</v>
       </c>
-      <c r="B8" s="185" t="s">
+      <c r="B8" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="185"/>
+      <c r="C8" s="203"/>
       <c r="D8" s="50">
         <f>D3-$D$6</f>
         <v>16527777.777777778</v>
@@ -6565,18 +6564,18 @@
         <f t="shared" ref="E8:E43" si="0">D8/B$1</f>
         <v>3714.1073657927591</v>
       </c>
-      <c r="G8" s="192"/>
-      <c r="H8" s="193"/>
-      <c r="I8" s="194"/>
+      <c r="G8" s="188"/>
+      <c r="H8" s="189"/>
+      <c r="I8" s="190"/>
     </row>
     <row r="9" spans="1:9" ht="16.05" customHeight="1">
       <c r="A9" s="32">
         <v>46053</v>
       </c>
-      <c r="B9" s="185" t="s">
+      <c r="B9" s="203" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="185"/>
+      <c r="C9" s="203"/>
       <c r="D9" s="50">
         <f t="shared" ref="D9:D43" si="1">D8-$D$6</f>
         <v>16055555.555555556</v>
@@ -6585,18 +6584,18 @@
         <f t="shared" si="0"/>
         <v>3607.9900124843948</v>
       </c>
-      <c r="G9" s="192"/>
-      <c r="H9" s="193"/>
-      <c r="I9" s="194"/>
+      <c r="G9" s="188"/>
+      <c r="H9" s="189"/>
+      <c r="I9" s="190"/>
     </row>
     <row r="10" spans="1:9" ht="16.05" customHeight="1">
       <c r="A10" s="32">
         <v>46081</v>
       </c>
-      <c r="B10" s="185" t="s">
+      <c r="B10" s="203" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="185"/>
+      <c r="C10" s="203"/>
       <c r="D10" s="50">
         <f t="shared" si="1"/>
         <v>15583333.333333334</v>
@@ -6605,18 +6604,18 @@
         <f t="shared" si="0"/>
         <v>3501.8726591760301</v>
       </c>
-      <c r="G10" s="192"/>
-      <c r="H10" s="193"/>
-      <c r="I10" s="194"/>
+      <c r="G10" s="188"/>
+      <c r="H10" s="189"/>
+      <c r="I10" s="190"/>
     </row>
     <row r="11" spans="1:9" ht="16.05" customHeight="1">
       <c r="A11" s="32">
         <v>46112</v>
       </c>
-      <c r="B11" s="185" t="s">
+      <c r="B11" s="203" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="185"/>
+      <c r="C11" s="203"/>
       <c r="D11" s="50">
         <f t="shared" si="1"/>
         <v>15111111.111111112</v>
@@ -6625,18 +6624,18 @@
         <f t="shared" si="0"/>
         <v>3395.7553058676658</v>
       </c>
-      <c r="G11" s="192"/>
-      <c r="H11" s="193"/>
-      <c r="I11" s="194"/>
+      <c r="G11" s="188"/>
+      <c r="H11" s="189"/>
+      <c r="I11" s="190"/>
     </row>
     <row r="12" spans="1:9" ht="16.05" customHeight="1">
       <c r="A12" s="32">
         <v>46142</v>
       </c>
-      <c r="B12" s="185" t="s">
+      <c r="B12" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="185"/>
+      <c r="C12" s="203"/>
       <c r="D12" s="50">
         <f t="shared" si="1"/>
         <v>14638888.88888889</v>
@@ -6645,18 +6644,18 @@
         <f t="shared" si="0"/>
         <v>3289.6379525593011</v>
       </c>
-      <c r="G12" s="192"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="194"/>
+      <c r="G12" s="188"/>
+      <c r="H12" s="189"/>
+      <c r="I12" s="190"/>
     </row>
     <row r="13" spans="1:9" ht="16.05" customHeight="1">
       <c r="A13" s="32">
         <v>46173</v>
       </c>
-      <c r="B13" s="185" t="s">
+      <c r="B13" s="203" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="185"/>
+      <c r="C13" s="203"/>
       <c r="D13" s="50">
         <f t="shared" si="1"/>
         <v>14166666.666666668</v>
@@ -6665,18 +6664,18 @@
         <f t="shared" si="0"/>
         <v>3183.5205992509368</v>
       </c>
-      <c r="G13" s="192"/>
-      <c r="H13" s="193"/>
-      <c r="I13" s="194"/>
+      <c r="G13" s="188"/>
+      <c r="H13" s="189"/>
+      <c r="I13" s="190"/>
     </row>
     <row r="14" spans="1:9" ht="16.05" customHeight="1">
       <c r="A14" s="32">
         <v>46203</v>
       </c>
-      <c r="B14" s="185" t="s">
+      <c r="B14" s="203" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="185"/>
+      <c r="C14" s="203"/>
       <c r="D14" s="50">
         <f t="shared" si="1"/>
         <v>13694444.444444446</v>
@@ -6685,18 +6684,18 @@
         <f t="shared" si="0"/>
         <v>3077.4032459425721</v>
       </c>
-      <c r="G14" s="192"/>
-      <c r="H14" s="193"/>
-      <c r="I14" s="194"/>
+      <c r="G14" s="188"/>
+      <c r="H14" s="189"/>
+      <c r="I14" s="190"/>
     </row>
     <row r="15" spans="1:9" ht="16.05" customHeight="1">
       <c r="A15" s="32">
         <v>46234</v>
       </c>
-      <c r="B15" s="185" t="s">
+      <c r="B15" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="185"/>
+      <c r="C15" s="203"/>
       <c r="D15" s="50">
         <f t="shared" si="1"/>
         <v>13222222.222222224</v>
@@ -6705,18 +6704,18 @@
         <f t="shared" si="0"/>
         <v>2971.2858926342078</v>
       </c>
-      <c r="G15" s="192"/>
-      <c r="H15" s="193"/>
-      <c r="I15" s="194"/>
+      <c r="G15" s="188"/>
+      <c r="H15" s="189"/>
+      <c r="I15" s="190"/>
     </row>
     <row r="16" spans="1:9" ht="16.05" customHeight="1">
       <c r="A16" s="32">
         <v>46265</v>
       </c>
-      <c r="B16" s="185" t="s">
+      <c r="B16" s="203" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="185"/>
+      <c r="C16" s="203"/>
       <c r="D16" s="50">
         <f t="shared" si="1"/>
         <v>12750000.000000002</v>
@@ -6725,18 +6724,18 @@
         <f t="shared" si="0"/>
         <v>2865.1685393258431</v>
       </c>
-      <c r="G16" s="192"/>
-      <c r="H16" s="193"/>
-      <c r="I16" s="194"/>
+      <c r="G16" s="188"/>
+      <c r="H16" s="189"/>
+      <c r="I16" s="190"/>
     </row>
     <row r="17" spans="1:9" ht="16.05" customHeight="1">
       <c r="A17" s="32">
         <v>46295</v>
       </c>
-      <c r="B17" s="185" t="s">
+      <c r="B17" s="203" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="185"/>
+      <c r="C17" s="203"/>
       <c r="D17" s="50">
         <f t="shared" si="1"/>
         <v>12277777.77777778</v>
@@ -6745,18 +6744,18 @@
         <f t="shared" si="0"/>
         <v>2759.0511860174788</v>
       </c>
-      <c r="G17" s="192"/>
-      <c r="H17" s="193"/>
-      <c r="I17" s="194"/>
+      <c r="G17" s="188"/>
+      <c r="H17" s="189"/>
+      <c r="I17" s="190"/>
     </row>
     <row r="18" spans="1:9" ht="16.05" customHeight="1">
       <c r="A18" s="32">
         <v>46326</v>
       </c>
-      <c r="B18" s="185" t="s">
+      <c r="B18" s="203" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="185"/>
+      <c r="C18" s="203"/>
       <c r="D18" s="50">
         <f t="shared" si="1"/>
         <v>11805555.555555558</v>
@@ -6765,18 +6764,18 @@
         <f t="shared" si="0"/>
         <v>2652.9338327091141</v>
       </c>
-      <c r="G18" s="192"/>
-      <c r="H18" s="193"/>
-      <c r="I18" s="194"/>
+      <c r="G18" s="188"/>
+      <c r="H18" s="189"/>
+      <c r="I18" s="190"/>
     </row>
     <row r="19" spans="1:9" ht="16.05" customHeight="1">
       <c r="A19" s="32">
         <v>46356</v>
       </c>
-      <c r="B19" s="185" t="s">
+      <c r="B19" s="203" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="185"/>
+      <c r="C19" s="203"/>
       <c r="D19" s="50">
         <f t="shared" si="1"/>
         <v>11333333.333333336</v>
@@ -6785,18 +6784,18 @@
         <f t="shared" si="0"/>
         <v>2546.8164794007498</v>
       </c>
-      <c r="G19" s="192"/>
-      <c r="H19" s="193"/>
-      <c r="I19" s="194"/>
+      <c r="G19" s="188"/>
+      <c r="H19" s="189"/>
+      <c r="I19" s="190"/>
     </row>
     <row r="20" spans="1:9" ht="16.05" customHeight="1">
       <c r="A20" s="32">
         <v>46387</v>
       </c>
-      <c r="B20" s="185" t="s">
+      <c r="B20" s="203" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="185"/>
+      <c r="C20" s="203"/>
       <c r="D20" s="50">
         <f t="shared" si="1"/>
         <v>10861111.111111114</v>
@@ -6805,18 +6804,18 @@
         <f t="shared" si="0"/>
         <v>2440.6991260923851</v>
       </c>
-      <c r="G20" s="192"/>
-      <c r="H20" s="193"/>
-      <c r="I20" s="194"/>
+      <c r="G20" s="188"/>
+      <c r="H20" s="189"/>
+      <c r="I20" s="190"/>
     </row>
     <row r="21" spans="1:9" ht="16.05" customHeight="1">
       <c r="A21" s="32">
         <v>46418</v>
       </c>
-      <c r="B21" s="185" t="s">
+      <c r="B21" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="185"/>
+      <c r="C21" s="203"/>
       <c r="D21" s="50">
         <f t="shared" si="1"/>
         <v>10388888.888888892</v>
@@ -6825,18 +6824,18 @@
         <f t="shared" si="0"/>
         <v>2334.5817727840208</v>
       </c>
-      <c r="G21" s="192"/>
-      <c r="H21" s="193"/>
-      <c r="I21" s="194"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="189"/>
+      <c r="I21" s="190"/>
     </row>
     <row r="22" spans="1:9" ht="16.05" customHeight="1">
       <c r="A22" s="32">
         <v>46446</v>
       </c>
-      <c r="B22" s="185" t="s">
+      <c r="B22" s="203" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="185"/>
+      <c r="C22" s="203"/>
       <c r="D22" s="50">
         <f t="shared" si="1"/>
         <v>9916666.6666666698</v>
@@ -6845,18 +6844,18 @@
         <f t="shared" si="0"/>
         <v>2228.4644194756561</v>
       </c>
-      <c r="G22" s="192"/>
-      <c r="H22" s="193"/>
-      <c r="I22" s="194"/>
+      <c r="G22" s="188"/>
+      <c r="H22" s="189"/>
+      <c r="I22" s="190"/>
     </row>
     <row r="23" spans="1:9" ht="16.05" customHeight="1">
       <c r="A23" s="32">
         <v>46477</v>
       </c>
-      <c r="B23" s="185" t="s">
+      <c r="B23" s="203" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="185"/>
+      <c r="C23" s="203"/>
       <c r="D23" s="50">
         <f t="shared" si="1"/>
         <v>9444444.4444444478</v>
@@ -6865,18 +6864,18 @@
         <f t="shared" si="0"/>
         <v>2122.3470661672918</v>
       </c>
-      <c r="G23" s="192"/>
-      <c r="H23" s="193"/>
-      <c r="I23" s="194"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="189"/>
+      <c r="I23" s="190"/>
     </row>
     <row r="24" spans="1:9" ht="16.05" customHeight="1">
       <c r="A24" s="32">
         <v>46507</v>
       </c>
-      <c r="B24" s="185" t="s">
+      <c r="B24" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="185"/>
+      <c r="C24" s="203"/>
       <c r="D24" s="50">
         <f t="shared" si="1"/>
         <v>8972222.2222222257</v>
@@ -6885,18 +6884,18 @@
         <f t="shared" si="0"/>
         <v>2016.2297128589271</v>
       </c>
-      <c r="G24" s="192"/>
-      <c r="H24" s="193"/>
-      <c r="I24" s="194"/>
+      <c r="G24" s="188"/>
+      <c r="H24" s="189"/>
+      <c r="I24" s="190"/>
     </row>
     <row r="25" spans="1:9" ht="16.05" customHeight="1">
       <c r="A25" s="32">
         <v>46538</v>
       </c>
-      <c r="B25" s="185" t="s">
+      <c r="B25" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="185"/>
+      <c r="C25" s="203"/>
       <c r="D25" s="50">
         <f t="shared" si="1"/>
         <v>8500000.0000000037</v>
@@ -6905,18 +6904,18 @@
         <f t="shared" si="0"/>
         <v>1910.1123595505626</v>
       </c>
-      <c r="G25" s="192"/>
-      <c r="H25" s="193"/>
-      <c r="I25" s="194"/>
+      <c r="G25" s="188"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="190"/>
     </row>
     <row r="26" spans="1:9" ht="16.05" customHeight="1">
       <c r="A26" s="32">
         <v>46568</v>
       </c>
-      <c r="B26" s="185" t="s">
+      <c r="B26" s="203" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="185"/>
+      <c r="C26" s="203"/>
       <c r="D26" s="50">
         <f t="shared" si="1"/>
         <v>8027777.7777777817</v>
@@ -6925,18 +6924,18 @@
         <f t="shared" si="0"/>
         <v>1803.9950062421981</v>
       </c>
-      <c r="G26" s="192"/>
-      <c r="H26" s="193"/>
-      <c r="I26" s="194"/>
+      <c r="G26" s="188"/>
+      <c r="H26" s="189"/>
+      <c r="I26" s="190"/>
     </row>
     <row r="27" spans="1:9" ht="16.05" customHeight="1">
       <c r="A27" s="32">
         <v>46599</v>
       </c>
-      <c r="B27" s="185" t="s">
+      <c r="B27" s="203" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="185"/>
+      <c r="C27" s="203"/>
       <c r="D27" s="50">
         <f t="shared" si="1"/>
         <v>7555555.5555555597</v>
@@ -6945,18 +6944,18 @@
         <f t="shared" si="0"/>
         <v>1697.8776529338336</v>
       </c>
-      <c r="G27" s="192"/>
-      <c r="H27" s="193"/>
-      <c r="I27" s="194"/>
+      <c r="G27" s="188"/>
+      <c r="H27" s="189"/>
+      <c r="I27" s="190"/>
     </row>
     <row r="28" spans="1:9" ht="16.05" customHeight="1" thickBot="1">
       <c r="A28" s="32">
         <v>46630</v>
       </c>
-      <c r="B28" s="185" t="s">
+      <c r="B28" s="203" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="185"/>
+      <c r="C28" s="203"/>
       <c r="D28" s="50">
         <f t="shared" si="1"/>
         <v>7083333.3333333377</v>
@@ -6965,18 +6964,18 @@
         <f t="shared" si="0"/>
         <v>1591.7602996254691</v>
       </c>
-      <c r="G28" s="195"/>
-      <c r="H28" s="196"/>
-      <c r="I28" s="197"/>
+      <c r="G28" s="191"/>
+      <c r="H28" s="192"/>
+      <c r="I28" s="193"/>
     </row>
     <row r="29" spans="1:9" ht="16.05" customHeight="1">
       <c r="A29" s="32">
         <v>46660</v>
       </c>
-      <c r="B29" s="185" t="s">
+      <c r="B29" s="203" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="185"/>
+      <c r="C29" s="203"/>
       <c r="D29" s="50">
         <f t="shared" si="1"/>
         <v>6611111.1111111157</v>
@@ -6985,14 +6984,14 @@
         <f t="shared" si="0"/>
         <v>1485.6429463171046</v>
       </c>
-      <c r="G29" s="201" t="s">
+      <c r="G29" s="197" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="203">
+      <c r="H29" s="199">
         <f>SUM(H32:H43)</f>
         <v>11232000</v>
       </c>
-      <c r="I29" s="205">
+      <c r="I29" s="201">
         <f>SUM(I32:I43)</f>
         <v>2524.0449438202249</v>
       </c>
@@ -7001,10 +7000,10 @@
       <c r="A30" s="32">
         <v>46691</v>
       </c>
-      <c r="B30" s="185" t="s">
+      <c r="B30" s="203" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="185"/>
+      <c r="C30" s="203"/>
       <c r="D30" s="50">
         <f t="shared" si="1"/>
         <v>6138888.8888888936</v>
@@ -7013,18 +7012,18 @@
         <f t="shared" si="0"/>
         <v>1379.5255930087401</v>
       </c>
-      <c r="G30" s="202"/>
-      <c r="H30" s="204"/>
-      <c r="I30" s="206"/>
+      <c r="G30" s="198"/>
+      <c r="H30" s="200"/>
+      <c r="I30" s="202"/>
     </row>
     <row r="31" spans="1:9" ht="16.95" customHeight="1" thickBot="1">
       <c r="A31" s="32">
         <v>46721</v>
       </c>
-      <c r="B31" s="185" t="s">
+      <c r="B31" s="203" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="185"/>
+      <c r="C31" s="203"/>
       <c r="D31" s="50">
         <f t="shared" si="1"/>
         <v>5666666.6666666716</v>
@@ -7033,18 +7032,18 @@
         <f t="shared" si="0"/>
         <v>1273.4082397003756</v>
       </c>
-      <c r="G31" s="198"/>
-      <c r="H31" s="199"/>
-      <c r="I31" s="200"/>
+      <c r="G31" s="194"/>
+      <c r="H31" s="195"/>
+      <c r="I31" s="196"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="32">
         <v>46752</v>
       </c>
-      <c r="B32" s="185" t="s">
+      <c r="B32" s="203" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="185"/>
+      <c r="C32" s="203"/>
       <c r="D32" s="50">
         <f t="shared" si="1"/>
         <v>5194444.4444444496</v>
@@ -7070,10 +7069,10 @@
       <c r="A33" s="32">
         <v>46783</v>
       </c>
-      <c r="B33" s="185" t="s">
+      <c r="B33" s="203" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="185"/>
+      <c r="C33" s="203"/>
       <c r="D33" s="50">
         <f t="shared" si="1"/>
         <v>4722222.2222222276</v>
@@ -7099,10 +7098,10 @@
       <c r="A34" s="32">
         <v>46812</v>
       </c>
-      <c r="B34" s="185" t="s">
+      <c r="B34" s="203" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="185"/>
+      <c r="C34" s="203"/>
       <c r="D34" s="50">
         <f t="shared" si="1"/>
         <v>4250000.0000000056</v>
@@ -7127,10 +7126,10 @@
       <c r="A35" s="32">
         <v>46843</v>
       </c>
-      <c r="B35" s="185" t="s">
+      <c r="B35" s="203" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="185"/>
+      <c r="C35" s="203"/>
       <c r="D35" s="50">
         <f t="shared" si="1"/>
         <v>3777777.7777777836</v>
@@ -7155,10 +7154,10 @@
       <c r="A36" s="32">
         <v>46873</v>
       </c>
-      <c r="B36" s="185" t="s">
+      <c r="B36" s="203" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="185"/>
+      <c r="C36" s="203"/>
       <c r="D36" s="50">
         <f t="shared" si="1"/>
         <v>3305555.5555555616</v>
@@ -7183,10 +7182,10 @@
       <c r="A37" s="32">
         <v>46904</v>
       </c>
-      <c r="B37" s="185" t="s">
+      <c r="B37" s="203" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="185"/>
+      <c r="C37" s="203"/>
       <c r="D37" s="50">
         <f t="shared" si="1"/>
         <v>2833333.3333333395</v>
@@ -7211,10 +7210,10 @@
       <c r="A38" s="32">
         <v>46934</v>
       </c>
-      <c r="B38" s="185" t="s">
+      <c r="B38" s="203" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="185"/>
+      <c r="C38" s="203"/>
       <c r="D38" s="50">
         <f t="shared" si="1"/>
         <v>2361111.1111111175</v>
@@ -7239,10 +7238,10 @@
       <c r="A39" s="32">
         <v>46965</v>
       </c>
-      <c r="B39" s="185" t="s">
+      <c r="B39" s="203" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="185"/>
+      <c r="C39" s="203"/>
       <c r="D39" s="50">
         <f t="shared" si="1"/>
         <v>1888888.8888888953</v>
@@ -7267,10 +7266,10 @@
       <c r="A40" s="32">
         <v>46996</v>
       </c>
-      <c r="B40" s="185" t="s">
+      <c r="B40" s="203" t="s">
         <v>73</v>
       </c>
-      <c r="C40" s="185"/>
+      <c r="C40" s="203"/>
       <c r="D40" s="50">
         <f t="shared" si="1"/>
         <v>1416666.666666673</v>
@@ -7295,10 +7294,10 @@
       <c r="A41" s="32">
         <v>47026</v>
       </c>
-      <c r="B41" s="185" t="s">
+      <c r="B41" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="185"/>
+      <c r="C41" s="203"/>
       <c r="D41" s="50">
         <f t="shared" si="1"/>
         <v>944444.44444445078</v>
@@ -7323,10 +7322,10 @@
       <c r="A42" s="32">
         <v>47057</v>
       </c>
-      <c r="B42" s="185" t="s">
+      <c r="B42" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="185"/>
+      <c r="C42" s="203"/>
       <c r="D42" s="50">
         <f t="shared" si="1"/>
         <v>472222.22222222853</v>
@@ -7351,10 +7350,10 @@
       <c r="A43" s="32">
         <v>47087</v>
       </c>
-      <c r="B43" s="185" t="s">
+      <c r="B43" s="203" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="185"/>
+      <c r="C43" s="203"/>
       <c r="D43" s="50">
         <f t="shared" si="1"/>
         <v>6.28642737865448E-9</v>
@@ -7377,18 +7376,28 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="G4:I28"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
@@ -7401,28 +7410,18 @@
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="G4:I28"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="I29:I30"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7467,42 +7466,42 @@
       <c r="C1" s="27">
         <v>4450</v>
       </c>
-      <c r="D1" s="144" t="s">
+      <c r="D1" s="177" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="145"/>
+      <c r="E1" s="178"/>
       <c r="F1" s="124">
         <v>10</v>
       </c>
-      <c r="G1" s="147" t="s">
+      <c r="G1" s="180" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="148"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="181"/>
       <c r="K1" s="43"/>
-      <c r="L1" s="152" t="s">
+      <c r="L1" s="184" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
+      <c r="M1" s="184"/>
+      <c r="N1" s="184"/>
+      <c r="O1" s="184"/>
+      <c r="P1" s="184"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="155"/>
-      <c r="B2" s="155"/>
-      <c r="C2" s="156"/>
+      <c r="A2" s="175"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="176"/>
       <c r="D2" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="154" t="s">
+      <c r="G2" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="154"/>
+      <c r="H2" s="145"/>
       <c r="I2" s="29">
         <f>5000*30</f>
         <v>150000</v>
@@ -7512,11 +7511,11 @@
         <v>33.707865168539328</v>
       </c>
       <c r="K2" s="43"/>
-      <c r="L2" s="151" t="s">
+      <c r="L2" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
+      <c r="M2" s="183"/>
+      <c r="N2" s="183"/>
       <c r="O2" s="25" t="s">
         <v>7</v>
       </c>
@@ -7525,11 +7524,11 @@
       </c>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="153" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="153"/>
+      <c r="A3" s="161" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
       <c r="D3" s="11">
         <v>17000000</v>
       </c>
@@ -7538,10 +7537,10 @@
         <v>3820.2247191011238</v>
       </c>
       <c r="F3" s="12"/>
-      <c r="G3" s="154" t="s">
+      <c r="G3" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="154"/>
+      <c r="H3" s="145"/>
       <c r="I3" s="29">
         <v>100000</v>
       </c>
@@ -7550,11 +7549,11 @@
         <v>22.471910112359552</v>
       </c>
       <c r="K3" s="43"/>
-      <c r="L3" s="150" t="s">
+      <c r="L3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="150"/>
-      <c r="N3" s="150"/>
+      <c r="M3" s="167"/>
+      <c r="N3" s="167"/>
       <c r="O3" s="3">
         <v>200000</v>
       </c>
@@ -7564,11 +7563,11 @@
       </c>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="153"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="161"/>
       <c r="D4" s="11">
         <v>66000</v>
       </c>
@@ -7576,10 +7575,10 @@
         <f>D4/$C$1</f>
         <v>14.831460674157304</v>
       </c>
-      <c r="G4" s="154" t="s">
+      <c r="G4" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="154"/>
+      <c r="H4" s="145"/>
       <c r="I4" s="29">
         <v>65000</v>
       </c>
@@ -7588,11 +7587,11 @@
         <v>14.606741573033707</v>
       </c>
       <c r="K4" s="43"/>
-      <c r="L4" s="150" t="s">
+      <c r="L4" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="150"/>
-      <c r="N4" s="150"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
       <c r="O4" s="3">
         <f>54000*3</f>
         <v>162000</v>
@@ -7603,11 +7602,11 @@
       </c>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="161" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
       <c r="D5" s="11">
         <v>50000</v>
       </c>
@@ -7615,10 +7614,10 @@
         <f>D5/$C$1</f>
         <v>11.235955056179776</v>
       </c>
-      <c r="G5" s="154" t="s">
+      <c r="G5" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="154"/>
+      <c r="H5" s="145"/>
       <c r="I5" s="29">
         <f>(D4*5%)*26</f>
         <v>85800</v>
@@ -7628,11 +7627,11 @@
         <v>19.280898876404493</v>
       </c>
       <c r="K5" s="43"/>
-      <c r="L5" s="150" t="s">
+      <c r="L5" s="167" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="167"/>
       <c r="O5" s="3">
         <v>100000</v>
       </c>
@@ -7642,11 +7641,11 @@
       </c>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
       <c r="D6" s="11">
         <f>(D4*26)</f>
         <v>1716000</v>
@@ -7655,10 +7654,10 @@
         <f>D6/$C$1</f>
         <v>385.61797752808991</v>
       </c>
-      <c r="G6" s="146" t="s">
+      <c r="G6" s="179" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="146"/>
+      <c r="H6" s="179"/>
       <c r="I6" s="19">
         <f>SUM(I1:I5)</f>
         <v>400800</v>
@@ -7668,11 +7667,11 @@
         <v>90.067415730337075</v>
       </c>
       <c r="K6" s="43"/>
-      <c r="L6" s="150" t="s">
+      <c r="L6" s="167" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="150"/>
-      <c r="N6" s="150"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
       <c r="O6" s="3">
         <v>300000</v>
       </c>
@@ -7682,11 +7681,11 @@
       </c>
     </row>
     <row r="7" spans="1:22" s="14" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="161" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="153"/>
-      <c r="C7" s="153"/>
+      <c r="B7" s="161"/>
+      <c r="C7" s="161"/>
       <c r="D7" s="11">
         <f>(D4*26)+(D5*4)</f>
         <v>1916000</v>
@@ -7700,11 +7699,11 @@
         <v>38202.247191011236</v>
       </c>
       <c r="K7" s="44"/>
-      <c r="L7" s="150" t="s">
+      <c r="L7" s="167" t="s">
         <v>164</v>
       </c>
-      <c r="M7" s="150"/>
-      <c r="N7" s="150"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
       <c r="O7" s="3">
         <v>500000</v>
       </c>
@@ -7719,11 +7718,11 @@
         <f>SUM(F15:F20)</f>
         <v>38200</v>
       </c>
-      <c r="G8" s="149" t="s">
+      <c r="G8" s="182" t="s">
         <v>161</v>
       </c>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
       <c r="J8" s="18">
         <f>('Crédit Banque'!B7)/7</f>
         <v>1505952.3809523808</v>
@@ -7732,11 +7731,11 @@
         <f>J8/$C$1</f>
         <v>338.41626538255747</v>
       </c>
-      <c r="L8" s="168" t="s">
+      <c r="L8" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="169"/>
-      <c r="N8" s="170"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="174"/>
       <c r="O8" s="19">
         <f>SUM(O3:O7)</f>
         <v>1262000</v>
@@ -7758,81 +7757,81 @@
       <c r="S9" s="8"/>
     </row>
     <row r="10" spans="1:22" s="14" customFormat="1" ht="16.05" customHeight="1" thickBot="1">
-      <c r="A10" s="178" t="s">
+      <c r="A10" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="179"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="179"/>
-      <c r="E10" s="179"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="179"/>
-      <c r="H10" s="179"/>
-      <c r="I10" s="179"/>
-      <c r="J10" s="179"/>
-      <c r="K10" s="179"/>
-      <c r="L10" s="179"/>
-      <c r="M10" s="179"/>
-      <c r="N10" s="180"/>
-      <c r="P10" s="161" t="s">
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="153"/>
+      <c r="N10" s="154"/>
+      <c r="P10" s="164" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="162"/>
-      <c r="R10" s="162"/>
-      <c r="S10" s="162"/>
-      <c r="T10" s="163"/>
+      <c r="Q10" s="165"/>
+      <c r="R10" s="165"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="166"/>
     </row>
     <row r="11" spans="1:22" ht="28.05" customHeight="1">
-      <c r="A11" s="157" t="s">
+      <c r="A11" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="181" t="s">
+      <c r="B11" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="183" t="s">
+      <c r="C11" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="171" t="s">
+      <c r="D11" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="171"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="171"/>
-      <c r="L11" s="172" t="s">
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="146" t="s">
         <v>116</v>
       </c>
-      <c r="M11" s="174" t="s">
+      <c r="M11" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="176" t="s">
+      <c r="N11" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="O11" s="167"/>
-      <c r="P11" s="157" t="s">
+      <c r="O11" s="171"/>
+      <c r="P11" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="Q11" s="159" t="s">
+      <c r="Q11" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="164" t="s">
+      <c r="R11" s="168" t="s">
         <v>22</v>
       </c>
-      <c r="S11" s="164" t="s">
+      <c r="S11" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="T11" s="165" t="s">
+      <c r="T11" s="169" t="s">
         <v>24</v>
       </c>
       <c r="V11" s="17"/>
     </row>
     <row r="12" spans="1:22" ht="62.4">
-      <c r="A12" s="158"/>
-      <c r="B12" s="182"/>
-      <c r="C12" s="184"/>
+      <c r="A12" s="156"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="160"/>
       <c r="D12" s="13" t="s">
         <v>31</v>
       </c>
@@ -7861,15 +7860,15 @@
       <c r="K12" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="173"/>
-      <c r="M12" s="175"/>
-      <c r="N12" s="177"/>
-      <c r="O12" s="167"/>
-      <c r="P12" s="158"/>
-      <c r="Q12" s="160"/>
-      <c r="R12" s="159"/>
-      <c r="S12" s="159"/>
-      <c r="T12" s="166"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="149"/>
+      <c r="N12" s="151"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="156"/>
+      <c r="Q12" s="163"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="162"/>
+      <c r="T12" s="170"/>
       <c r="V12" s="17"/>
     </row>
     <row r="13" spans="1:22">
@@ -10173,25 +10172,13 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="P10:T10"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="L7:N7"/>
@@ -10203,13 +10190,25 @@
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:K11"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="P10:T10"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="L2:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
